--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BCEC1A-55E6-0F44-B633-5D915372DFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890EC6BB-3B8C-354A-B984-149CF9FD717A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="248">
   <si>
     <t>Length_f</t>
   </si>
@@ -1101,6 +1101,9 @@
   </si>
   <si>
     <t>SD7062</t>
+  </si>
+  <si>
+    <t>NACA0021</t>
   </si>
 </sst>
 </file>
@@ -5642,6 +5645,42 @@
       <c r="AP8" s="10">
         <v>1.7520000000000001E-2</v>
       </c>
+      <c r="AQ8" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="AS8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="AY8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -6069,6 +6108,21 @@
       </c>
       <c r="C8">
         <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
     <row r="21" s="21" customFormat="1" x14ac:dyDescent="0.2"/>

--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890EC6BB-3B8C-354A-B984-149CF9FD717A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13397B9D-C140-8D4B-BA24-9660E53132B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -4299,7 +4299,7 @@
         <v>21.527799999999999</v>
       </c>
       <c r="P8" s="4">
-        <v>1.64</v>
+        <v>4.76</v>
       </c>
       <c r="Q8" s="4">
         <v>0</v>
@@ -4312,6 +4312,70 @@
       </c>
       <c r="T8" s="4">
         <v>1.4</v>
+      </c>
+      <c r="U8" s="4">
+        <v>6.7270000000000003</v>
+      </c>
+      <c r="V8" s="4">
+        <f>U8*2</f>
+        <v>13.454000000000001</v>
+      </c>
+      <c r="W8" s="4">
+        <v>3</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>2.9950000000000001</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5701,6 +5765,10 @@
     <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" customWidth="1"/>
+    <col min="15" max="15" width="12.5" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
@@ -6123,6 +6191,15 @@
       </c>
       <c r="H8">
         <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0.9</v>
+      </c>
+      <c r="O8">
+        <v>0.9</v>
+      </c>
+      <c r="P8">
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" s="21" customFormat="1" x14ac:dyDescent="0.2"/>

--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/Initial_Design_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13397B9D-C140-8D4B-BA24-9660E53132B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8C7738-ED36-DD42-9F34-AD6A3751ECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="245">
   <si>
     <t>Length_f</t>
   </si>
@@ -1005,15 +1005,6 @@
   </si>
   <si>
     <t>NACA2412</t>
-  </si>
-  <si>
-    <t>B747</t>
-  </si>
-  <si>
-    <t>T38</t>
-  </si>
-  <si>
-    <t>BACJ</t>
   </si>
   <si>
     <t>NACA 0010</t>
@@ -2250,7 +2241,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -3197,7 +3188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADD393-55AB-49FB-9382-D2896E9EB980}">
-  <dimension ref="A1:AV21"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="4"/>
@@ -3385,7 +3376,7 @@
         <v>4.5</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H8" si="0">F2/G2</f>
+        <f t="shared" ref="H2:H6" si="0">F2/G2</f>
         <v>10.333333333333334</v>
       </c>
       <c r="I2" s="4">
@@ -3514,7 +3505,7 @@
         <v>213</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -3658,39 +3649,38 @@
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="E4" s="4">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="F4" s="4">
-        <v>231.83</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4">
-        <v>21.3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>10.884037558685446</v>
+        <v>6.75</v>
       </c>
       <c r="I4" s="4">
-        <f>PI()*(G4/2)^2</f>
-        <v>356.32729275178838</v>
+        <v>12.56</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4">
-        <v>13000</v>
+        <v>280</v>
       </c>
       <c r="L4" s="4">
         <v>1</v>
@@ -3699,46 +3689,43 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>5500</v>
+        <v>174</v>
       </c>
       <c r="O4" s="4">
-        <f>2*N4</f>
-        <v>11000</v>
+        <v>380</v>
       </c>
       <c r="P4" s="4">
-        <v>7</v>
+        <v>7.32</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.25</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="R4" s="4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="S4" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T4" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="U4" s="4">
-        <f>V4/2</f>
-        <v>1244.3080500000001</v>
+        <v>36.6</v>
       </c>
       <c r="V4" s="4">
-        <v>2488.6161000000002</v>
+        <v>80</v>
       </c>
       <c r="W4" s="4">
-        <f>(70^2)/U4</f>
-        <v>3.9379316078522515</v>
+        <v>3.5</v>
       </c>
       <c r="X4" s="4">
-        <v>0.2</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y4" s="4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="4">
-        <v>18.3</v>
+        <v>3.61</v>
       </c>
       <c r="AA4" s="4">
         <v>1.1000000000000001</v>
@@ -3765,23 +3752,22 @@
         <v>0</v>
       </c>
       <c r="AI4" s="4">
-        <v>908</v>
+        <v>11.2</v>
       </c>
       <c r="AJ4" s="4">
-        <f>AI4*2</f>
-        <v>1816</v>
+        <v>25</v>
       </c>
       <c r="AK4" s="4">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL4" s="4">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AM4" s="4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="4">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="4">
         <v>1.1000000000000001</v>
@@ -3810,38 +3796,40 @@
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="4">
         <v>0.6</v>
       </c>
-      <c r="E5" s="4">
-        <v>1.05</v>
-      </c>
       <c r="F5" s="4">
-        <v>43.08</v>
+        <v>57</v>
       </c>
       <c r="G5" s="4">
-        <v>4.5999999999999996</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3652173913043484</v>
+        <v>5.7</v>
       </c>
       <c r="I5" s="4">
-        <v>16.600000000000001</v>
+        <f>PI()*(G5/2)^2</f>
+        <v>78.539816339744831</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
       </c>
       <c r="K5" s="4">
-        <v>793</v>
+        <f>2500</f>
+        <v>2500</v>
       </c>
       <c r="L5" s="4">
         <v>1</v>
@@ -3850,45 +3838,43 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>170</v>
+        <v>301</v>
       </c>
       <c r="O5" s="4">
-        <f>2*170</f>
-        <v>340</v>
+        <v>620</v>
       </c>
       <c r="P5" s="4">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="R5" s="4">
-        <v>31.8</v>
+        <v>0</v>
       </c>
       <c r="S5" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T5" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="U5" s="4">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="V5" s="4">
-        <f>2*59</f>
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="W5" s="4">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="X5" s="4">
-        <v>0.33</v>
+        <v>0.9</v>
       </c>
       <c r="Y5" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="4">
-        <v>4.5999999999999996</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="4">
         <v>1.1000000000000001</v>
@@ -3915,23 +3901,22 @@
         <v>0</v>
       </c>
       <c r="AI5" s="4">
-        <v>41.42</v>
+        <v>100</v>
       </c>
       <c r="AJ5" s="4">
-        <f>2*AI5</f>
-        <v>82.84</v>
+        <v>140</v>
       </c>
       <c r="AK5" s="4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL5" s="4">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="AM5" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="4">
-        <v>5.85</v>
+        <v>7</v>
       </c>
       <c r="AO5" s="4">
         <v>1.1000000000000001</v>
@@ -3959,57 +3944,60 @@
       </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>220</v>
+      <c r="A6" t="s">
+        <v>242</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>0.18</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="E6" s="4">
-        <v>0.3</v>
+        <v>0.20810000000000001</v>
       </c>
       <c r="F6" s="4">
-        <v>27</v>
+        <v>3.9470000000000001</v>
       </c>
       <c r="G6" s="4">
-        <v>4</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>8.0223577235772368</v>
       </c>
       <c r="I6" s="4">
-        <v>12.56</v>
+        <f>PI()*(G6/2)^2</f>
+        <v>0.19011662102463991</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
       </c>
       <c r="K6" s="4">
-        <v>280</v>
+        <f>F6*G6</f>
+        <v>1.941924</v>
       </c>
       <c r="L6" s="4">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>174</v>
+        <v>10.7639</v>
       </c>
       <c r="O6" s="4">
-        <v>380</v>
+        <f>2*N6</f>
+        <v>21.527799999999999</v>
       </c>
       <c r="P6" s="4">
-        <v>7.32</v>
+        <v>4.76</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.67200000000000004</v>
+        <v>0</v>
       </c>
       <c r="R6" s="4">
         <v>0</v>
@@ -4018,28 +4006,29 @@
         <v>0</v>
       </c>
       <c r="T6" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="U6" s="4">
-        <v>36.6</v>
+        <v>6.7270000000000003</v>
       </c>
       <c r="V6" s="4">
-        <v>80</v>
+        <f>U6*2</f>
+        <v>13.454000000000001</v>
       </c>
       <c r="W6" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="X6" s="4">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="4">
         <v>0</v>
       </c>
       <c r="Z6" s="4">
-        <v>3.61</v>
+        <v>1.498</v>
       </c>
       <c r="AA6" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" s="4">
         <v>0</v>
@@ -4063,10 +4052,11 @@
         <v>0</v>
       </c>
       <c r="AI6" s="4">
-        <v>11.2</v>
+        <v>1.4962</v>
       </c>
       <c r="AJ6" s="4">
-        <v>25</v>
+        <f>2*AI6</f>
+        <v>2.9923999999999999</v>
       </c>
       <c r="AK6" s="4">
         <v>1.6</v>
@@ -4078,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="AN6" s="4">
-        <v>4</v>
+        <v>0.37140000000000001</v>
       </c>
       <c r="AO6" s="4">
         <v>1.1000000000000001</v>
@@ -4105,280 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="F7" s="4">
-        <v>57</v>
-      </c>
-      <c r="G7" s="4">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="0"/>
-        <v>5.7</v>
-      </c>
-      <c r="I7" s="4">
-        <f>PI()*(G7/2)^2</f>
-        <v>78.539816339744831</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4">
-        <f>2500</f>
-        <v>2500</v>
-      </c>
-      <c r="L7" s="4">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4">
-        <v>2</v>
-      </c>
-      <c r="N7" s="4">
-        <v>301</v>
-      </c>
-      <c r="O7" s="4">
-        <v>620</v>
-      </c>
-      <c r="P7" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U7" s="4">
-        <v>180</v>
-      </c>
-      <c r="V7" s="4">
-        <v>200</v>
-      </c>
-      <c r="W7" s="4">
-        <v>3</v>
-      </c>
-      <c r="X7" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="4">
-        <v>100</v>
-      </c>
-      <c r="AJ7" s="4">
-        <v>140</v>
-      </c>
-      <c r="AK7" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="AL7" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="AM7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="4">
-        <v>7</v>
-      </c>
-      <c r="AO7" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3.9470000000000001</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="H8" s="4">
-        <f t="shared" si="0"/>
-        <v>8.0223577235772368</v>
-      </c>
-      <c r="I8" s="4">
-        <f>PI()*(G8/2)^2</f>
-        <v>0.19011662102463991</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <f>F8*G8</f>
-        <v>1.941924</v>
-      </c>
-      <c r="L8" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M8" s="4">
-        <v>2</v>
-      </c>
-      <c r="N8" s="4">
-        <v>10.7639</v>
-      </c>
-      <c r="O8" s="4">
-        <f>2*N8</f>
-        <v>21.527799999999999</v>
-      </c>
-      <c r="P8" s="4">
-        <v>4.76</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="U8" s="4">
-        <v>6.7270000000000003</v>
-      </c>
-      <c r="V8" s="4">
-        <f>U8*2</f>
-        <v>13.454000000000001</v>
-      </c>
-      <c r="W8" s="4">
-        <v>3</v>
-      </c>
-      <c r="X8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>2.9950000000000001</v>
-      </c>
-      <c r="AA8" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="AB8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -4388,7 +4105,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B20</xm:sqref>
+          <xm:sqref>B2:B18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4398,7 +4115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538960B4-04F0-4DA1-BF31-3569558CC234}">
-  <dimension ref="A1:BB21"/>
+  <dimension ref="A1:BB19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="10" customWidth="1"/>
@@ -4914,139 +4631,143 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:54" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="str">
         <f>Main_Input!A4</f>
-        <v>B747</v>
+        <v>Electric</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C4" s="10">
-        <v>0.10100000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="D4" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-0.35049999999999998</v>
-      </c>
-      <c r="F4" s="10">
-        <v>-0.25140000000000001</v>
-      </c>
-      <c r="G4" s="10">
-        <v>-0.14929999999999999</v>
-      </c>
-      <c r="H4" s="10">
-        <v>-3.1800000000000002E-2</v>
-      </c>
-      <c r="I4" s="10">
-        <v>9.1200000000000003E-2</v>
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="3">
+        <f>-0.483</f>
+        <v>-0.48299999999999998</v>
+      </c>
+      <c r="F4" s="29">
+        <f>-0.3983</f>
+        <v>-0.39829999999999999</v>
+      </c>
+      <c r="G4" s="29">
+        <f>-0.3108</f>
+        <v>-0.31080000000000002</v>
+      </c>
+      <c r="H4" s="29">
+        <v>-0.2485</v>
+      </c>
+      <c r="I4" s="29">
+        <v>-0.1244</v>
       </c>
       <c r="J4" s="10">
-        <v>0.21329999999999999</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0.30480000000000002</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0.318</v>
-      </c>
-      <c r="M4" s="10">
-        <v>0.39250000000000002</v>
-      </c>
-      <c r="N4" s="10">
-        <v>0.4889</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0.58550000000000002</v>
-      </c>
-      <c r="P4" s="10">
-        <v>0.68079999999999996</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>0.77439999999999998</v>
+        <v>-5.8900000000000001E-2</v>
+      </c>
+      <c r="K4" s="29">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="L4" s="29">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="M4" s="29">
+        <v>0.45279999999999998</v>
+      </c>
+      <c r="N4" s="29">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="O4" s="29">
+        <v>0.7429</v>
+      </c>
+      <c r="P4" s="29">
+        <v>0.85670000000000002</v>
+      </c>
+      <c r="Q4" s="29">
+        <v>0.95979999999999999</v>
       </c>
       <c r="R4" s="10">
-        <v>0.87209999999999999</v>
+        <v>1.0251999999999999</v>
       </c>
       <c r="S4" s="10">
-        <v>0.97289999999999999</v>
-      </c>
-      <c r="T4" s="10">
-        <v>1.0609999999999999</v>
-      </c>
-      <c r="U4" s="10">
-        <v>1.1263000000000001</v>
+        <v>1.0969</v>
+      </c>
+      <c r="T4" s="29">
+        <v>1.1591</v>
+      </c>
+      <c r="U4" s="29">
+        <v>1.1391</v>
       </c>
       <c r="V4" s="10">
-        <v>0.91649999999999998</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="W4" s="10">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X4">
-        <v>9.5300000000000003E-3</v>
-      </c>
-      <c r="Y4">
-        <v>8.5199999999999998E-3</v>
-      </c>
-      <c r="Z4">
-        <v>7.4099999999999999E-3</v>
-      </c>
-      <c r="AA4">
-        <v>5.8399999999999997E-3</v>
-      </c>
-      <c r="AB4">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="AC4">
-        <v>5.0899999999999999E-3</v>
-      </c>
-      <c r="AD4">
-        <v>5.0600000000000003E-3</v>
-      </c>
-      <c r="AE4">
-        <v>7.43E-3</v>
-      </c>
-      <c r="AF4">
-        <v>9.4800000000000006E-3</v>
-      </c>
-      <c r="AG4">
-        <v>1.0330000000000001E-2</v>
-      </c>
-      <c r="AH4">
-        <v>1.132E-2</v>
-      </c>
-      <c r="AI4">
-        <v>1.256E-2</v>
-      </c>
-      <c r="AJ4">
-        <v>1.4409999999999999E-2</v>
-      </c>
-      <c r="AK4">
-        <v>1.634E-2</v>
-      </c>
-      <c r="AL4">
-        <v>2.052E-2</v>
-      </c>
-      <c r="AM4">
-        <v>2.4979999999999999E-2</v>
-      </c>
-      <c r="AN4">
-        <v>3.1119999999999998E-2</v>
-      </c>
-      <c r="AO4">
-        <v>7.1559999999999999E-2</v>
-      </c>
-      <c r="AP4" s="10">
-        <v>5.0600000000000003E-3</v>
+        <f>1.1591</f>
+        <v>1.1591</v>
+      </c>
+      <c r="X4" s="29">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="Y4" s="29">
+        <v>2.6689999999999998E-2</v>
+      </c>
+      <c r="Z4" s="29">
+        <v>2.6689999999999998E-2</v>
+      </c>
+      <c r="AA4" s="29">
+        <v>2.1329999999999998E-2</v>
+      </c>
+      <c r="AB4" s="29">
+        <v>2.1909999999999999E-2</v>
+      </c>
+      <c r="AC4" s="29">
+        <v>2.4060000000000002E-2</v>
+      </c>
+      <c r="AD4" s="29">
+        <v>2.81E-2</v>
+      </c>
+      <c r="AE4" s="29">
+        <v>3.099E-2</v>
+      </c>
+      <c r="AF4" s="29">
+        <v>3.304E-2</v>
+      </c>
+      <c r="AG4" s="29">
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="AH4" s="29">
+        <v>3.2559999999999999E-2</v>
+      </c>
+      <c r="AI4" s="29">
+        <v>3.159E-2</v>
+      </c>
+      <c r="AJ4" s="29">
+        <v>3.0269999999999998E-2</v>
+      </c>
+      <c r="AK4" s="11">
+        <v>3.245E-2</v>
+      </c>
+      <c r="AL4" s="11">
+        <v>3.9794999999999997E-2</v>
+      </c>
+      <c r="AM4" s="29">
+        <v>4.9970000000000001E-2</v>
+      </c>
+      <c r="AN4" s="29">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="AO4" s="11">
+        <v>9.2009999999999995E-2</v>
+      </c>
+      <c r="AP4" s="29">
+        <v>2.1329999999999998E-2</v>
       </c>
       <c r="AQ4" s="10" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="AR4" s="10">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="AS4" s="10">
         <v>0.3</v>
@@ -5061,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="AW4" s="10" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="AX4" s="10">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="AY4" s="10">
         <v>0.3</v>
@@ -5082,130 +4803,134 @@
     <row r="5" spans="1:54" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="str">
         <f>Main_Input!A5</f>
-        <v>T38</v>
+        <v>Tiltrotor Turboprop</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C5" s="10">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="D5" s="10">
         <v>0.3</v>
       </c>
-      <c r="E5" s="29">
-        <v>-0.54879999999999995</v>
+      <c r="E5" s="3">
+        <f>-0.483</f>
+        <v>-0.48299999999999998</v>
       </c>
       <c r="F5" s="29">
-        <v>-0.44479999999999997</v>
+        <f>-0.3983</f>
+        <v>-0.39829999999999999</v>
       </c>
       <c r="G5" s="29">
-        <v>-0.34029999999999999</v>
+        <f>-0.3108</f>
+        <v>-0.31080000000000002</v>
       </c>
       <c r="H5" s="29">
-        <v>-0.23960000000000001</v>
+        <v>-0.2485</v>
       </c>
       <c r="I5" s="29">
-        <v>-0.12509999999999999</v>
+        <v>-0.1244</v>
       </c>
       <c r="J5" s="10">
-        <v>0</v>
+        <v>-5.8900000000000001E-2</v>
       </c>
       <c r="K5" s="29">
-        <v>0.12509999999999999</v>
+        <v>0.13750000000000001</v>
       </c>
       <c r="L5" s="29">
-        <v>0.2394</v>
+        <v>0.30249999999999999</v>
       </c>
       <c r="M5" s="29">
-        <v>0.34010000000000001</v>
+        <v>0.45279999999999998</v>
       </c>
       <c r="N5" s="29">
-        <v>0.4446</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="O5" s="29">
-        <v>0.54869999999999997</v>
+        <v>0.7429</v>
       </c>
       <c r="P5" s="29">
-        <v>0.6462</v>
+        <v>0.85670000000000002</v>
       </c>
       <c r="Q5" s="29">
-        <v>0.73480000000000001</v>
+        <v>0.95979999999999999</v>
       </c>
       <c r="R5" s="10">
-        <v>0.8</v>
+        <v>1.0251999999999999</v>
       </c>
       <c r="S5" s="10">
-        <v>0.93</v>
+        <v>1.0969</v>
       </c>
       <c r="T5" s="29">
-        <v>0.71640000000000004</v>
+        <v>1.1591</v>
       </c>
       <c r="U5" s="29">
-        <v>0.71740000000000004</v>
+        <v>1.1391</v>
       </c>
       <c r="V5" s="10">
-        <v>0.7</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="W5" s="10">
-        <v>0.93</v>
+        <f>1.1591</f>
+        <v>1.1591</v>
       </c>
       <c r="X5" s="29">
-        <v>9.9399999999999992E-3</v>
+        <v>3.1399999999999997E-2</v>
       </c>
       <c r="Y5" s="29">
-        <v>8.1200000000000005E-3</v>
+        <v>2.6689999999999998E-2</v>
       </c>
       <c r="Z5" s="29">
-        <v>7.3699999999999998E-3</v>
+        <v>2.6689999999999998E-2</v>
       </c>
       <c r="AA5" s="29">
-        <v>5.7000000000000002E-3</v>
+        <v>2.1329999999999998E-2</v>
       </c>
       <c r="AB5" s="29">
-        <v>4.2599999999999999E-3</v>
+        <v>2.1909999999999999E-2</v>
       </c>
       <c r="AC5" s="29">
-        <v>3.3800000000000002E-3</v>
+        <v>2.4060000000000002E-2</v>
       </c>
       <c r="AD5" s="29">
-        <v>4.2599999999999999E-3</v>
+        <v>2.81E-2</v>
       </c>
       <c r="AE5" s="29">
-        <v>5.7000000000000002E-3</v>
+        <v>3.099E-2</v>
       </c>
       <c r="AF5" s="29">
-        <v>7.3699999999999998E-3</v>
+        <v>3.304E-2</v>
       </c>
       <c r="AG5" s="29">
-        <v>8.1200000000000005E-3</v>
+        <v>3.3750000000000002E-2</v>
       </c>
       <c r="AH5" s="29">
-        <v>9.9600000000000001E-3</v>
+        <v>3.2559999999999999E-2</v>
       </c>
       <c r="AI5" s="29">
-        <v>0.01</v>
+        <v>3.159E-2</v>
       </c>
       <c r="AJ5" s="29">
-        <v>2.034E-2</v>
+        <v>3.0269999999999998E-2</v>
       </c>
       <c r="AK5" s="11">
-        <v>0.03</v>
+        <v>3.245E-2</v>
       </c>
       <c r="AL5" s="11">
-        <v>0.05</v>
+        <v>3.9794999999999997E-2</v>
       </c>
       <c r="AM5" s="29">
-        <v>0.1191</v>
+        <v>4.9970000000000001E-2</v>
       </c>
       <c r="AN5" s="29">
-        <v>0.12388</v>
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="AO5" s="11">
-        <v>0.15</v>
+        <v>9.2009999999999995E-2</v>
       </c>
       <c r="AP5" s="29">
-        <v>3.3800000000000002E-3</v>
+        <v>2.1329999999999998E-2</v>
       </c>
       <c r="AQ5" s="10" t="s">
         <v>181</v>
@@ -5244,143 +4969,138 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:54" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="str">
-        <f>Main_Input!A6</f>
-        <v>Electric</v>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>242</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C6" s="10">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D6" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="E6" s="3">
-        <f>-0.483</f>
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="F6" s="29">
-        <f>-0.3983</f>
-        <v>-0.39829999999999999</v>
-      </c>
-      <c r="G6" s="29">
-        <f>-0.3108</f>
-        <v>-0.31080000000000002</v>
-      </c>
-      <c r="H6" s="29">
-        <v>-0.2485</v>
-      </c>
-      <c r="I6" s="29">
-        <v>-0.1244</v>
+        <v>0.255</v>
+      </c>
+      <c r="E6" s="10">
+        <v>-0.1431</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.20549999999999999</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0.29360000000000003</v>
       </c>
       <c r="J6" s="10">
-        <v>-5.8900000000000001E-2</v>
-      </c>
-      <c r="K6" s="29">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="L6" s="29">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="M6" s="29">
-        <v>0.45279999999999998</v>
-      </c>
-      <c r="N6" s="29">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="O6" s="29">
-        <v>0.7429</v>
-      </c>
-      <c r="P6" s="29">
-        <v>0.85670000000000002</v>
-      </c>
-      <c r="Q6" s="29">
-        <v>0.95979999999999999</v>
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0.55389999999999995</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0.6593</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0.76270000000000004</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0.86850000000000005</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0.97030000000000005</v>
+      </c>
+      <c r="P6" s="10">
+        <v>1.0701000000000001</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>1.1707000000000001</v>
       </c>
       <c r="R6" s="10">
-        <v>1.0251999999999999</v>
+        <v>1.2575000000000001</v>
       </c>
       <c r="S6" s="10">
-        <v>1.0969</v>
-      </c>
-      <c r="T6" s="29">
-        <v>1.1591</v>
-      </c>
-      <c r="U6" s="29">
-        <v>1.1391</v>
+        <v>1.3427</v>
+      </c>
+      <c r="T6" s="10">
+        <v>1.4209000000000001</v>
+      </c>
+      <c r="U6" s="10">
+        <v>1.4866999999999999</v>
       </c>
       <c r="V6" s="10">
-        <v>1.0009999999999999</v>
+        <v>1.5385</v>
       </c>
       <c r="W6" s="10">
-        <f>1.1591</f>
-        <v>1.1591</v>
-      </c>
-      <c r="X6" s="29">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Y6" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="Z6" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="AA6" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AB6" s="29">
-        <v>2.1909999999999999E-2</v>
-      </c>
-      <c r="AC6" s="29">
-        <v>2.4060000000000002E-2</v>
-      </c>
-      <c r="AD6" s="29">
-        <v>2.81E-2</v>
-      </c>
-      <c r="AE6" s="29">
-        <v>3.099E-2</v>
-      </c>
-      <c r="AF6" s="29">
-        <v>3.304E-2</v>
-      </c>
-      <c r="AG6" s="29">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="AH6" s="29">
-        <v>3.2559999999999999E-2</v>
-      </c>
-      <c r="AI6" s="29">
-        <v>3.159E-2</v>
-      </c>
-      <c r="AJ6" s="29">
-        <v>3.0269999999999998E-2</v>
-      </c>
-      <c r="AK6" s="11">
-        <v>3.245E-2</v>
-      </c>
-      <c r="AL6" s="11">
-        <v>3.9794999999999997E-2</v>
-      </c>
-      <c r="AM6" s="29">
-        <v>4.9970000000000001E-2</v>
-      </c>
-      <c r="AN6" s="29">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="AO6" s="11">
-        <v>9.2009999999999995E-2</v>
-      </c>
-      <c r="AP6" s="29">
-        <v>2.1329999999999998E-2</v>
+        <v>1.5978000000000001</v>
+      </c>
+      <c r="X6" s="10">
+        <v>3.032E-2</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>2.435E-2</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>1.8790000000000001E-2</v>
+      </c>
+      <c r="AB6" s="10">
+        <v>1.8429999999999998E-2</v>
+      </c>
+      <c r="AC6" s="10">
+        <v>1.7649999999999999E-2</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>1.7919999999999998E-2</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>1.84E-2</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>1.9290000000000002E-2</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>2.018E-2</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>2.147E-2</v>
+      </c>
+      <c r="AI6" s="10">
+        <v>2.2919999999999999E-2</v>
+      </c>
+      <c r="AJ6" s="10">
+        <v>2.4580000000000001E-2</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>2.6849999999999999E-2</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>2.9309999999999999E-2</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>3.2190000000000003E-2</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>3.567E-2</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>3.9809999999999998E-2</v>
+      </c>
+      <c r="AP6" s="10">
+        <v>1.7520000000000001E-2</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="AR6" s="10">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="AS6" s="10">
         <v>0.3</v>
@@ -5395,10 +5115,10 @@
         <v>0</v>
       </c>
       <c r="AW6" s="10" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="AX6" s="10">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AY6" s="10">
         <v>0.3</v>
@@ -5413,340 +5133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:54" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="str">
-        <f>Main_Input!A7</f>
-        <v>Tiltrotor Turboprop</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="E7" s="3">
-        <f>-0.483</f>
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="F7" s="29">
-        <f>-0.3983</f>
-        <v>-0.39829999999999999</v>
-      </c>
-      <c r="G7" s="29">
-        <f>-0.3108</f>
-        <v>-0.31080000000000002</v>
-      </c>
-      <c r="H7" s="29">
-        <v>-0.2485</v>
-      </c>
-      <c r="I7" s="29">
-        <v>-0.1244</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-5.8900000000000001E-2</v>
-      </c>
-      <c r="K7" s="29">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="L7" s="29">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="M7" s="29">
-        <v>0.45279999999999998</v>
-      </c>
-      <c r="N7" s="29">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="O7" s="29">
-        <v>0.7429</v>
-      </c>
-      <c r="P7" s="29">
-        <v>0.85670000000000002</v>
-      </c>
-      <c r="Q7" s="29">
-        <v>0.95979999999999999</v>
-      </c>
-      <c r="R7" s="10">
-        <v>1.0251999999999999</v>
-      </c>
-      <c r="S7" s="10">
-        <v>1.0969</v>
-      </c>
-      <c r="T7" s="29">
-        <v>1.1591</v>
-      </c>
-      <c r="U7" s="29">
-        <v>1.1391</v>
-      </c>
-      <c r="V7" s="10">
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="W7" s="10">
-        <f>1.1591</f>
-        <v>1.1591</v>
-      </c>
-      <c r="X7" s="29">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Y7" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="Z7" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="AA7" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AB7" s="29">
-        <v>2.1909999999999999E-2</v>
-      </c>
-      <c r="AC7" s="29">
-        <v>2.4060000000000002E-2</v>
-      </c>
-      <c r="AD7" s="29">
-        <v>2.81E-2</v>
-      </c>
-      <c r="AE7" s="29">
-        <v>3.099E-2</v>
-      </c>
-      <c r="AF7" s="29">
-        <v>3.304E-2</v>
-      </c>
-      <c r="AG7" s="29">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="AH7" s="29">
-        <v>3.2559999999999999E-2</v>
-      </c>
-      <c r="AI7" s="29">
-        <v>3.159E-2</v>
-      </c>
-      <c r="AJ7" s="29">
-        <v>3.0269999999999998E-2</v>
-      </c>
-      <c r="AK7" s="11">
-        <v>3.245E-2</v>
-      </c>
-      <c r="AL7" s="11">
-        <v>3.9794999999999997E-2</v>
-      </c>
-      <c r="AM7" s="29">
-        <v>4.9970000000000001E-2</v>
-      </c>
-      <c r="AN7" s="29">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="AO7" s="11">
-        <v>9.2009999999999995E-2</v>
-      </c>
-      <c r="AP7" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AQ7" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR7" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AS7" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AX7" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AY7" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ7" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0.255</v>
-      </c>
-      <c r="E8" s="10">
-        <v>-0.1431</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.10730000000000001</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0.20549999999999999</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0.29360000000000003</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0.44130000000000003</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0.55389999999999995</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0.6593</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0.76270000000000004</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0.86850000000000005</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0.97030000000000005</v>
-      </c>
-      <c r="P8" s="10">
-        <v>1.0701000000000001</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>1.1707000000000001</v>
-      </c>
-      <c r="R8" s="10">
-        <v>1.2575000000000001</v>
-      </c>
-      <c r="S8" s="10">
-        <v>1.3427</v>
-      </c>
-      <c r="T8" s="10">
-        <v>1.4209000000000001</v>
-      </c>
-      <c r="U8" s="10">
-        <v>1.4866999999999999</v>
-      </c>
-      <c r="V8" s="10">
-        <v>1.5385</v>
-      </c>
-      <c r="W8" s="10">
-        <v>1.5978000000000001</v>
-      </c>
-      <c r="X8" s="10">
-        <v>3.032E-2</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>2.435E-2</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>1.8790000000000001E-2</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>1.8429999999999998E-2</v>
-      </c>
-      <c r="AC8" s="10">
-        <v>1.7649999999999999E-2</v>
-      </c>
-      <c r="AD8" s="10">
-        <v>1.7919999999999998E-2</v>
-      </c>
-      <c r="AE8" s="10">
-        <v>1.84E-2</v>
-      </c>
-      <c r="AF8" s="10">
-        <v>1.9290000000000002E-2</v>
-      </c>
-      <c r="AG8" s="10">
-        <v>2.018E-2</v>
-      </c>
-      <c r="AH8" s="10">
-        <v>2.147E-2</v>
-      </c>
-      <c r="AI8" s="10">
-        <v>2.2919999999999999E-2</v>
-      </c>
-      <c r="AJ8" s="10">
-        <v>2.4580000000000001E-2</v>
-      </c>
-      <c r="AK8" s="10">
-        <v>2.6849999999999999E-2</v>
-      </c>
-      <c r="AL8" s="10">
-        <v>2.9309999999999999E-2</v>
-      </c>
-      <c r="AM8" s="10">
-        <v>3.2190000000000003E-2</v>
-      </c>
-      <c r="AN8" s="10">
-        <v>3.567E-2</v>
-      </c>
-      <c r="AO8" s="10">
-        <v>3.9809999999999998E-2</v>
-      </c>
-      <c r="AP8" s="10">
-        <v>1.7520000000000001E-2</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="AR8" s="10">
-        <v>0.21</v>
-      </c>
-      <c r="AS8" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="AX8" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="AY8" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ8" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5755,7 +5142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B77D4EB-A9CB-4E6A-B1A1-7AF90F186000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -5806,25 +5193,25 @@
         <v>167</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="M1" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="P1" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>223</v>
-      </c>
-      <c r="P1" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q1" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="R1" s="30" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -5890,7 +5277,7 @@
         <v>C172</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -5942,21 +5329,20 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="str">
-        <f>Main_Input!A4</f>
-        <v>B747</v>
+      <c r="A4" t="s">
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0.36799999999999999</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5968,73 +5354,72 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>200.47499999999999</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="str">
-        <f>Main_Input!A5</f>
-        <v>T38</v>
+      <c r="A5" t="s">
+        <v>240</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2455</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1.1399999999999999</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>6150</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -6057,7 +5442,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s">
         <v>188</v>
@@ -6080,21 +5465,6 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>160</v>
-      </c>
-      <c r="J6">
-        <v>0.39</v>
-      </c>
-      <c r="K6">
-        <v>0.8</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>275</v>
-      </c>
       <c r="N6">
         <v>0.9</v>
       </c>
@@ -6104,105 +5474,8 @@
       <c r="P6">
         <v>0.9</v>
       </c>
-      <c r="Q6">
-        <v>200.47499999999999</v>
-      </c>
-      <c r="R6">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>6150</v>
-      </c>
-      <c r="J7">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="K7">
-        <v>0.7</v>
-      </c>
-      <c r="L7">
-        <v>38</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0.9</v>
-      </c>
-      <c r="O8">
-        <v>0.9</v>
-      </c>
-      <c r="P8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="21" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="19" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6213,7 +5486,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B20</xm:sqref>
+          <xm:sqref>B2:B18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6273,78 +5546,78 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="28" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="28" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="28" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
